--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEA6723-6746-4E03-8FED-379372F5198A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666F93D-0F4F-4047-AF7D-E8144C800AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
   <si>
     <t>交易日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,10 +39,6 @@
   </si>
   <si>
     <t>股票名称</t>
-  </si>
-  <si>
-    <t>买入价(元)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>卖出价(元)</t>
@@ -774,6 +770,46 @@
   </si>
   <si>
     <t>初始本金（元）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亏损1R的卖出价</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>烽火通信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中长线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以为低点，想抄底的，结果炒到半山腰</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>成本价(元)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>豫能控股</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>算电协同，冲就完事了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -904,7 +940,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -941,6 +977,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1221,32 +1260,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T4"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="14.25" customWidth="1"/>
-    <col min="2" max="2" width="16.125" customWidth="1"/>
-    <col min="3" max="3" width="15.75" customWidth="1"/>
-    <col min="4" max="4" width="17" customWidth="1"/>
-    <col min="5" max="5" width="23.25" customWidth="1"/>
-    <col min="6" max="6" width="18.875" customWidth="1"/>
-    <col min="7" max="7" width="20.25" customWidth="1"/>
-    <col min="8" max="8" width="17.625" customWidth="1"/>
-    <col min="9" max="9" width="17.25" customWidth="1"/>
-    <col min="10" max="10" width="11.375" customWidth="1"/>
-    <col min="11" max="11" width="22.625" customWidth="1"/>
-    <col min="12" max="12" width="15" customWidth="1"/>
-    <col min="13" max="13" width="17.25" customWidth="1"/>
-    <col min="14" max="14" width="19.875" customWidth="1"/>
-    <col min="16" max="16" width="15.5" customWidth="1"/>
-    <col min="17" max="17" width="13.625" customWidth="1"/>
-    <col min="18" max="18" width="18.625" customWidth="1"/>
-    <col min="19" max="19" width="16.875" customWidth="1"/>
+    <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
+    <col min="2" max="2" width="16.125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
+    <col min="4" max="4" width="17" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.25" style="2" customWidth="1"/>
+    <col min="6" max="6" width="18.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.25" style="2" customWidth="1"/>
+    <col min="8" max="8" width="17.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.25" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.375" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22.625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="15" style="2" customWidth="1"/>
+    <col min="13" max="13" width="17.25" style="2" customWidth="1"/>
+    <col min="14" max="14" width="19.875" style="2" customWidth="1"/>
+    <col min="15" max="15" width="9" style="2"/>
+    <col min="16" max="17" width="15.5" style="2" customWidth="1"/>
+    <col min="18" max="18" width="13.625" style="2" customWidth="1"/>
+    <col min="19" max="19" width="18.625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="16.875" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1258,112 +1299,220 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="L1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="R1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="14">
-        <v>46107</v>
-      </c>
-      <c r="C2" s="1">
-        <v>690</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="16">
+        <v>46100</v>
+      </c>
+      <c r="C2" s="2">
+        <v>600498</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>97</v>
       </c>
       <c r="E2" s="1">
-        <v>5.8</v>
-      </c>
-      <c r="F2" s="1">
-        <v>6.49</v>
-      </c>
+        <v>43.886000000000003</v>
+      </c>
+      <c r="F2" s="1"/>
       <c r="G2" s="1">
-        <v>4100</v>
+        <v>600</v>
       </c>
       <c r="H2" s="1">
         <f>E2*G2</f>
-        <v>23780</v>
+        <v>26331.600000000002</v>
       </c>
       <c r="I2" s="1">
         <f>F2*G2</f>
-        <v>26609</v>
+        <v>0</v>
       </c>
       <c r="J2" s="1"/>
-      <c r="K2" s="1">
-        <f>IF(F2&lt;&gt;"",I2-H2-J2,"")</f>
-        <v>2829</v>
-      </c>
-      <c r="L2" s="1">
-        <f>IF(F2&lt;&gt;"",K2/H2*100,"")</f>
-        <v>11.896551724137931</v>
-      </c>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
       <c r="M2" s="1">
         <v>1500</v>
       </c>
-      <c r="N2" s="1">
+      <c r="N2" s="1" t="str">
         <f>IF(F2&lt;&gt;"",K2/M2,"")</f>
-        <v>1.8859999999999999</v>
+        <v/>
       </c>
       <c r="O2" s="1" t="str">
         <f>IF(F2&lt;&gt;"",IF(K2&gt;0,"盈","亏"),"")</f>
-        <v>盈</v>
-      </c>
-      <c r="P2" s="1">
+        <v/>
+      </c>
+      <c r="P2" s="1" t="str">
         <f>IF(F2&lt;&gt;"",IF(K2&gt;0,ABS(K2)/M2,ABS(K2)/M2),"")</f>
-        <v>1.8859999999999999</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>18</v>
+        <v/>
+      </c>
+      <c r="Q2" s="1">
+        <f>IF(E2&lt;&gt;"",(H2-J2-M2)/G2,"")</f>
+        <v>41.386000000000003</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="S2" s="1"/>
+        <v>98</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="T2" s="1"/>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" s="14">
+        <v>46107</v>
+      </c>
+      <c r="C3" s="1">
+        <v>690</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="1">
+        <v>5.8019999999999996</v>
+      </c>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1">
+        <v>4100</v>
+      </c>
+      <c r="H3" s="1">
+        <f>E3*G3</f>
+        <v>23788.199999999997</v>
+      </c>
+      <c r="I3" s="1">
+        <f>F3*G3</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="str">
+        <f>IF(F3&lt;&gt;"",I3-H3-J3,"")</f>
+        <v/>
+      </c>
+      <c r="L3" s="1" t="str">
+        <f>IF(F3&lt;&gt;"",K3/H3*100,"")</f>
+        <v/>
+      </c>
+      <c r="M3" s="1">
+        <v>1500</v>
+      </c>
+      <c r="N3" s="1" t="str">
+        <f>IF(F3&lt;&gt;"",K3/M3,"")</f>
+        <v/>
+      </c>
+      <c r="O3" s="1" t="str">
+        <f>IF(F3&lt;&gt;"",IF(K3&gt;0,"盈","亏"),"")</f>
+        <v/>
+      </c>
+      <c r="P3" s="1" t="str">
+        <f>IF(F3&lt;&gt;"",IF(K3&gt;0,ABS(K3)/M3,ABS(K3)/M3),"")</f>
+        <v/>
+      </c>
+      <c r="Q3" s="1">
+        <f>IF(E3&lt;&gt;"",(H3-J3-M3)/G3,"")</f>
+        <v>5.4361463414634139</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="T3" s="1"/>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B4" s="16">
+        <v>46108</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1896</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E4" s="2">
+        <v>15.624000000000001</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4300</v>
+      </c>
+      <c r="H4" s="1">
+        <f>E4*G4</f>
+        <v>67183.199999999997</v>
+      </c>
+      <c r="I4" s="1">
+        <f>F4*G4</f>
+        <v>0</v>
+      </c>
+      <c r="K4" s="1" t="str">
+        <f>IF(F4&lt;&gt;"",I4-H4-J4,"")</f>
+        <v/>
+      </c>
+      <c r="M4" s="2">
+        <v>2100</v>
+      </c>
+      <c r="Q4" s="1">
+        <f>IF(E4&lt;&gt;"",(H4-J4-M4)/G4,"")</f>
+        <v>15.135627906976744</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -1384,34 +1533,34 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <f>COUNTIF(交易记录!O:O,"盈")+COUNTIF(交易记录!O:O,"亏")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>COUNTIF(交易记录!O:O,"盈")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -1420,58 +1569,58 @@
         <v>0</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="str">
+        <f>IF(A2&gt;0,A3/A2*100,"0")</f>
+        <v>0</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5">
-        <f>IF(A2&gt;0,A3/A2*100,"0")</f>
-        <v>100</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <f>SUM(交易记录!K:K)</f>
-        <v>2829</v>
+        <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="3" t="str">
+        <f>IF(A2&gt;0,A6/A2,"0")</f>
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <f>IF(A2&gt;0,A6/A2,"0")</f>
-        <v>2829</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="str">
+        <f>IF(A3&gt;0,AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
-        <f>IF(A3&gt;0,AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
-        <v>1.8859999999999999</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
@@ -1480,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1492,58 +1641,58 @@
         <v>#DIV/0!</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="str">
+        <f>IF(A2&gt;0,(A5/100)*A8 - (1-A5/100)*A9,"0")</f>
+        <v>0</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2">
-        <f>IF(A2&gt;0,(A5/100)*A8 - (1-A5/100)*A9,"0")</f>
-        <v>1.8859999999999999</v>
-      </c>
-      <c r="B11" s="5" t="s">
+    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
+      <c r="A12" s="3" t="str">
+        <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M),"0")</f>
+        <v>0</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
-        <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M),"0")</f>
-        <v>2829</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <f>SUM(交易记录!N:N)</f>
-        <v>1.8859999999999999</v>
+        <v>0</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <f t="array" ref="A14">MAX(FREQUENCY(IF(交易记录!O:O="盈",ROW(交易记录!O:O)),IF(交易记录!O:O&lt;&gt;"盈",ROW(交易记录!O:O))))</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
@@ -1552,42 +1701,42 @@
         <v>0</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f>SUMIF(交易记录!F:F,"",交易记录!H:H)</f>
-        <v>0</v>
+        <v>117303</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
   </sheetData>
@@ -1614,54 +1763,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" t="s">
         <v>72</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>74</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -1681,7 +1830,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F3" s="10" t="e">
         <f>IF(E3&gt;0,E3/50000*100,"0")</f>
@@ -1713,7 +1862,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F4" s="10" t="e">
         <f t="shared" ref="F4:F14" si="1">IF(E4&gt;0,E4/50000*100,"0")</f>
@@ -1745,7 +1894,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F5" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1777,7 +1926,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F6" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1809,7 +1958,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F7" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1841,7 +1990,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F8" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1873,7 +2022,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F9" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1905,7 +2054,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1937,7 +2086,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="10" t="e">
         <f t="shared" si="1"/>
@@ -1969,7 +2118,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2001,7 +2150,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F13" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2033,7 +2182,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F14" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2068,12 +2217,12 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2">
         <v>50000</v>
@@ -2081,33 +2230,33 @@
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B3">
         <f>AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M)</f>
-        <v>1500</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>93</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
@@ -2116,15 +2265,15 @@
       </c>
       <c r="B7" s="10">
         <f>A7*$B$3</f>
-        <v>1500</v>
+        <v>1700</v>
       </c>
       <c r="C7" s="10">
         <f>$B$2-B7</f>
-        <v>48500</v>
+        <v>48300</v>
       </c>
       <c r="D7" s="10">
         <f>IF(C7&lt;$B$2,($B$2-C7)/C7*100,"0")</f>
-        <v>3.0927835051546393</v>
+        <v>3.5196687370600417</v>
       </c>
       <c r="E7" s="10" t="str">
         <f t="shared" ref="E7:E16" si="0">IF(D7&gt;10,"风险较高，需控制连续亏损次数","风险可控")</f>
@@ -2137,15 +2286,15 @@
       </c>
       <c r="B8" s="10">
         <f t="shared" ref="B8:B16" si="1">A8*$B$3</f>
-        <v>3000</v>
+        <v>3400</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" ref="C8:C16" si="2">$B$2-B8</f>
-        <v>47000</v>
+        <v>46600</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" ref="D8:D16" si="3">IF(C8&lt;$B$2,($B$2-C8)/C8*100,"0")</f>
-        <v>6.3829787234042552</v>
+        <v>7.296137339055794</v>
       </c>
       <c r="E8" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2158,19 +2307,19 @@
       </c>
       <c r="B9" s="10">
         <f t="shared" si="1"/>
-        <v>4500</v>
+        <v>5100</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
-        <v>45500</v>
+        <v>44900</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="3"/>
-        <v>9.8901098901098905</v>
+        <v>11.358574610244988</v>
       </c>
       <c r="E9" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>风险可控</v>
+        <v>风险较高，需控制连续亏损次数</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -2179,15 +2328,15 @@
       </c>
       <c r="B10" s="10">
         <f t="shared" si="1"/>
-        <v>6000</v>
+        <v>6800</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>44000</v>
+        <v>43200</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>13.636363636363635</v>
+        <v>15.74074074074074</v>
       </c>
       <c r="E10" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2200,15 +2349,15 @@
       </c>
       <c r="B11" s="10">
         <f t="shared" si="1"/>
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
-        <v>42500</v>
+        <v>41500</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="3"/>
-        <v>17.647058823529413</v>
+        <v>20.481927710843372</v>
       </c>
       <c r="E11" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2221,15 +2370,15 @@
       </c>
       <c r="B12" s="10">
         <f t="shared" si="1"/>
-        <v>9000</v>
+        <v>10200</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>41000</v>
+        <v>39800</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
-        <v>21.951219512195124</v>
+        <v>25.628140703517587</v>
       </c>
       <c r="E12" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2242,15 +2391,15 @@
       </c>
       <c r="B13" s="10">
         <f t="shared" si="1"/>
-        <v>10500</v>
+        <v>11900</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
-        <v>39500</v>
+        <v>38100</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="3"/>
-        <v>26.582278481012654</v>
+        <v>31.233595800524931</v>
       </c>
       <c r="E13" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2263,15 +2412,15 @@
       </c>
       <c r="B14" s="10">
         <f t="shared" si="1"/>
-        <v>12000</v>
+        <v>13600</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="2"/>
-        <v>38000</v>
+        <v>36400</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="3"/>
-        <v>31.578947368421051</v>
+        <v>37.362637362637365</v>
       </c>
       <c r="E14" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2284,15 +2433,15 @@
       </c>
       <c r="B15" s="10">
         <f t="shared" si="1"/>
-        <v>13500</v>
+        <v>15300</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" si="2"/>
-        <v>36500</v>
+        <v>34700</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="3"/>
-        <v>36.986301369863014</v>
+        <v>44.092219020172912</v>
       </c>
       <c r="E15" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2305,15 +2454,15 @@
       </c>
       <c r="B16" s="10">
         <f t="shared" si="1"/>
-        <v>15000</v>
+        <v>17000</v>
       </c>
       <c r="C16" s="10">
         <f t="shared" si="2"/>
-        <v>35000</v>
+        <v>33000</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="3"/>
-        <v>42.857142857142854</v>
+        <v>51.515151515151516</v>
       </c>
       <c r="E16" s="10" t="str">
         <f t="shared" si="0"/>

--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0666F93D-0F4F-4047-AF7D-E8144C800AB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9675F786-E8F9-4BE2-81E1-72DD2B5AF47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交易记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
   <si>
     <t>交易日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -810,6 +810,14 @@
   </si>
   <si>
     <t>算电协同，冲就完事了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不想持仓了，想空仓一段时间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电力板块走弱了，也超出了自己的盈亏R数了，果断清了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1347,7 +1355,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>96</v>
       </c>
@@ -1363,7 +1371,9 @@
       <c r="E2" s="1">
         <v>43.886000000000003</v>
       </c>
-      <c r="F2" s="1"/>
+      <c r="F2" s="1">
+        <v>47.75</v>
+      </c>
       <c r="G2" s="1">
         <v>600</v>
       </c>
@@ -1373,29 +1383,37 @@
       </c>
       <c r="I2" s="1">
         <f>F2*G2</f>
-        <v>0</v>
-      </c>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
+        <v>28650</v>
+      </c>
+      <c r="J2" s="1">
+        <v>37.54</v>
+      </c>
+      <c r="K2" s="1">
+        <f>IF(F2&lt;&gt;"",I2-H2-J2,"")</f>
+        <v>2280.8599999999979</v>
+      </c>
+      <c r="L2" s="11">
+        <f>IF(F2&lt;&gt;"",K2/H2*100,"")</f>
+        <v>8.6620638320496965</v>
+      </c>
       <c r="M2" s="1">
         <v>1500</v>
       </c>
-      <c r="N2" s="1" t="str">
+      <c r="N2" s="1">
         <f>IF(F2&lt;&gt;"",K2/M2,"")</f>
-        <v/>
+        <v>1.520573333333332</v>
       </c>
       <c r="O2" s="1" t="str">
         <f>IF(F2&lt;&gt;"",IF(K2&gt;0,"盈","亏"),"")</f>
-        <v/>
-      </c>
-      <c r="P2" s="1" t="str">
+        <v>盈</v>
+      </c>
+      <c r="P2" s="1">
         <f>IF(F2&lt;&gt;"",IF(K2&gt;0,ABS(K2)/M2,ABS(K2)/M2),"")</f>
-        <v/>
+        <v>1.520573333333332</v>
       </c>
       <c r="Q2" s="1">
         <f>IF(E2&lt;&gt;"",(H2-J2-M2)/G2,"")</f>
-        <v>41.386000000000003</v>
+        <v>41.323433333333334</v>
       </c>
       <c r="R2" s="1" t="s">
         <v>98</v>
@@ -1403,9 +1421,11 @@
       <c r="S2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="T2" s="1"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T2" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -1421,7 +1441,9 @@
       <c r="E3" s="1">
         <v>5.8019999999999996</v>
       </c>
-      <c r="F3" s="1"/>
+      <c r="F3" s="1">
+        <v>5.13</v>
+      </c>
       <c r="G3" s="1">
         <v>4100</v>
       </c>
@@ -1431,35 +1453,37 @@
       </c>
       <c r="I3" s="1">
         <f>F3*G3</f>
-        <v>0</v>
-      </c>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1" t="str">
+        <v>21033</v>
+      </c>
+      <c r="J3" s="1">
+        <v>7.47</v>
+      </c>
+      <c r="K3" s="1">
         <f>IF(F3&lt;&gt;"",I3-H3-J3,"")</f>
-        <v/>
-      </c>
-      <c r="L3" s="1" t="str">
-        <f>IF(F3&lt;&gt;"",K3/H3*100,"")</f>
-        <v/>
+        <v>-2762.6699999999969</v>
+      </c>
+      <c r="L3" s="11">
+        <f t="shared" ref="L3:L4" si="0">IF(F3&lt;&gt;"",K3/H3*100,"")</f>
+        <v>-11.61361515373167</v>
       </c>
       <c r="M3" s="1">
         <v>1500</v>
       </c>
-      <c r="N3" s="1" t="str">
+      <c r="N3" s="1">
         <f>IF(F3&lt;&gt;"",K3/M3,"")</f>
-        <v/>
+        <v>-1.841779999999998</v>
       </c>
       <c r="O3" s="1" t="str">
         <f>IF(F3&lt;&gt;"",IF(K3&gt;0,"盈","亏"),"")</f>
-        <v/>
-      </c>
-      <c r="P3" s="1" t="str">
+        <v>亏</v>
+      </c>
+      <c r="P3" s="1">
         <f>IF(F3&lt;&gt;"",IF(K3&gt;0,ABS(K3)/M3,ABS(K3)/M3),"")</f>
-        <v/>
+        <v>1.841779999999998</v>
       </c>
       <c r="Q3" s="1">
         <f>IF(E3&lt;&gt;"",(H3-J3-M3)/G3,"")</f>
-        <v>5.4361463414634139</v>
+        <v>5.4343243902439013</v>
       </c>
       <c r="R3" s="1" t="s">
         <v>17</v>
@@ -1467,9 +1491,11 @@
       <c r="S3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="T3" s="1"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="T3" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>101</v>
       </c>
@@ -1498,6 +1524,10 @@
       </c>
       <c r="K4" s="1" t="str">
         <f>IF(F4&lt;&gt;"",I4-H4-J4,"")</f>
+        <v/>
+      </c>
+      <c r="L4" s="11" t="str">
+        <f t="shared" si="0"/>
         <v/>
       </c>
       <c r="M4" s="2">
@@ -1542,7 +1572,7 @@
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <f>COUNTIF(交易记录!O:O,"盈")+COUNTIF(交易记录!O:O,"亏")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>23</v>
@@ -1554,7 +1584,7 @@
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>COUNTIF(交易记录!O:O,"盈")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -1566,7 +1596,7 @@
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <f>COUNTIF(交易记录!O:O,"亏")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>25</v>
@@ -1576,9 +1606,9 @@
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="str">
+      <c r="A5" s="5">
         <f>IF(A2&gt;0,A3/A2*100,"0")</f>
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>26</v>
@@ -1590,7 +1620,7 @@
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <f>SUM(交易记录!K:K)</f>
-        <v>0</v>
+        <v>-481.80999999999904</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -1600,9 +1630,9 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="str">
+      <c r="A7" s="3">
         <f>IF(A2&gt;0,A6/A2,"0")</f>
-        <v>0</v>
+        <v>-240.90499999999952</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>28</v>
@@ -1612,9 +1642,9 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="str">
+      <c r="A8" s="3">
         <f>IF(A3&gt;0,AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
-        <v>0</v>
+        <v>1.520573333333332</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>29</v>
@@ -1624,9 +1654,9 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="str">
+      <c r="A9" s="3">
         <f>IF(A4&gt;0,ABS(AVERAGEIF(交易记录!N:N,"&lt;0",交易记录!N:N)),"0")</f>
-        <v>0</v>
+        <v>1.841779999999998</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>30</v>
@@ -1636,9 +1666,9 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="e">
+      <c r="A10" s="3">
         <f>IF(A9&gt;0,A8/A9,"0")</f>
-        <v>#DIV/0!</v>
+        <v>0.8255998725870265</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>31</v>
@@ -1648,9 +1678,9 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="str">
+      <c r="A11" s="2">
         <f>IF(A2&gt;0,(A5/100)*A8 - (1-A5/100)*A9,"0")</f>
-        <v>0</v>
+        <v>-0.16060333333333299</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>32</v>
@@ -1660,9 +1690,9 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="str">
+      <c r="A12" s="3">
         <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M),"0")</f>
-        <v>0</v>
+        <v>-273.0256666666661</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>33</v>
@@ -1674,7 +1704,7 @@
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <f>SUM(交易记录!N:N)</f>
-        <v>0</v>
+        <v>-0.32120666666666597</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>34</v>
@@ -1686,7 +1716,7 @@
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <f t="array" ref="A14">MAX(FREQUENCY(IF(交易记录!O:O="盈",ROW(交易记录!O:O)),IF(交易记录!O:O&lt;&gt;"盈",ROW(交易记录!O:O))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>35</v>
@@ -1698,7 +1728,7 @@
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <f t="array" ref="A15">MAX(FREQUENCY(IF(交易记录!O:O="亏",ROW(交易记录!O:O)),IF(交易记录!O:O&lt;&gt;"亏",ROW(交易记录!O:O))))</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>36</v>
@@ -1718,7 +1748,7 @@
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
@@ -1730,7 +1760,7 @@
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f>SUMIF(交易记录!F:F,"",交易记录!H:H)</f>
-        <v>117303</v>
+        <v>67183.199999999997</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2225,7 +2255,7 @@
         <v>94</v>
       </c>
       <c r="B2">
-        <v>50000</v>
+        <v>70000</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
@@ -2233,8 +2263,7 @@
         <v>87</v>
       </c>
       <c r="B3">
-        <f>AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M)</f>
-        <v>1700</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -2265,15 +2294,15 @@
       </c>
       <c r="B7" s="10">
         <f>A7*$B$3</f>
-        <v>1700</v>
+        <v>2100</v>
       </c>
       <c r="C7" s="10">
         <f>$B$2-B7</f>
-        <v>48300</v>
+        <v>67900</v>
       </c>
       <c r="D7" s="10">
         <f>IF(C7&lt;$B$2,($B$2-C7)/C7*100,"0")</f>
-        <v>3.5196687370600417</v>
+        <v>3.0927835051546393</v>
       </c>
       <c r="E7" s="10" t="str">
         <f t="shared" ref="E7:E16" si="0">IF(D7&gt;10,"风险较高，需控制连续亏损次数","风险可控")</f>
@@ -2286,15 +2315,15 @@
       </c>
       <c r="B8" s="10">
         <f t="shared" ref="B8:B16" si="1">A8*$B$3</f>
-        <v>3400</v>
+        <v>4200</v>
       </c>
       <c r="C8" s="10">
         <f t="shared" ref="C8:C16" si="2">$B$2-B8</f>
-        <v>46600</v>
+        <v>65800</v>
       </c>
       <c r="D8" s="10">
         <f t="shared" ref="D8:D16" si="3">IF(C8&lt;$B$2,($B$2-C8)/C8*100,"0")</f>
-        <v>7.296137339055794</v>
+        <v>6.3829787234042552</v>
       </c>
       <c r="E8" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2307,19 +2336,19 @@
       </c>
       <c r="B9" s="10">
         <f t="shared" si="1"/>
-        <v>5100</v>
+        <v>6300</v>
       </c>
       <c r="C9" s="10">
         <f t="shared" si="2"/>
-        <v>44900</v>
+        <v>63700</v>
       </c>
       <c r="D9" s="10">
         <f t="shared" si="3"/>
-        <v>11.358574610244988</v>
+        <v>9.8901098901098905</v>
       </c>
       <c r="E9" s="10" t="str">
         <f t="shared" si="0"/>
-        <v>风险较高，需控制连续亏损次数</v>
+        <v>风险可控</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
@@ -2328,15 +2357,15 @@
       </c>
       <c r="B10" s="10">
         <f t="shared" si="1"/>
-        <v>6800</v>
+        <v>8400</v>
       </c>
       <c r="C10" s="10">
         <f t="shared" si="2"/>
-        <v>43200</v>
+        <v>61600</v>
       </c>
       <c r="D10" s="10">
         <f t="shared" si="3"/>
-        <v>15.74074074074074</v>
+        <v>13.636363636363635</v>
       </c>
       <c r="E10" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2349,15 +2378,15 @@
       </c>
       <c r="B11" s="10">
         <f t="shared" si="1"/>
-        <v>8500</v>
+        <v>10500</v>
       </c>
       <c r="C11" s="10">
         <f t="shared" si="2"/>
-        <v>41500</v>
+        <v>59500</v>
       </c>
       <c r="D11" s="10">
         <f t="shared" si="3"/>
-        <v>20.481927710843372</v>
+        <v>17.647058823529413</v>
       </c>
       <c r="E11" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2370,15 +2399,15 @@
       </c>
       <c r="B12" s="10">
         <f t="shared" si="1"/>
-        <v>10200</v>
+        <v>12600</v>
       </c>
       <c r="C12" s="10">
         <f t="shared" si="2"/>
-        <v>39800</v>
+        <v>57400</v>
       </c>
       <c r="D12" s="10">
         <f t="shared" si="3"/>
-        <v>25.628140703517587</v>
+        <v>21.951219512195124</v>
       </c>
       <c r="E12" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2391,15 +2420,15 @@
       </c>
       <c r="B13" s="10">
         <f t="shared" si="1"/>
-        <v>11900</v>
+        <v>14700</v>
       </c>
       <c r="C13" s="10">
         <f t="shared" si="2"/>
-        <v>38100</v>
+        <v>55300</v>
       </c>
       <c r="D13" s="10">
         <f t="shared" si="3"/>
-        <v>31.233595800524931</v>
+        <v>26.582278481012654</v>
       </c>
       <c r="E13" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2412,15 +2441,15 @@
       </c>
       <c r="B14" s="10">
         <f t="shared" si="1"/>
-        <v>13600</v>
+        <v>16800</v>
       </c>
       <c r="C14" s="10">
         <f t="shared" si="2"/>
-        <v>36400</v>
+        <v>53200</v>
       </c>
       <c r="D14" s="10">
         <f t="shared" si="3"/>
-        <v>37.362637362637365</v>
+        <v>31.578947368421051</v>
       </c>
       <c r="E14" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2433,15 +2462,15 @@
       </c>
       <c r="B15" s="10">
         <f t="shared" si="1"/>
-        <v>15300</v>
+        <v>18900</v>
       </c>
       <c r="C15" s="10">
         <f t="shared" si="2"/>
-        <v>34700</v>
+        <v>51100</v>
       </c>
       <c r="D15" s="10">
         <f t="shared" si="3"/>
-        <v>44.092219020172912</v>
+        <v>36.986301369863014</v>
       </c>
       <c r="E15" s="10" t="str">
         <f t="shared" si="0"/>
@@ -2454,15 +2483,15 @@
       </c>
       <c r="B16" s="10">
         <f t="shared" si="1"/>
-        <v>17000</v>
+        <v>21000</v>
       </c>
       <c r="C16" s="10">
         <f t="shared" si="2"/>
-        <v>33000</v>
+        <v>49000</v>
       </c>
       <c r="D16" s="10">
         <f t="shared" si="3"/>
-        <v>51.515151515151516</v>
+        <v>42.857142857142854</v>
       </c>
       <c r="E16" s="10" t="str">
         <f t="shared" si="0"/>

--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9675F786-E8F9-4BE2-81E1-72DD2B5AF47C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55ADDBE-20C6-4709-A434-0E6EBE39D3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交易记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
   <si>
     <t>交易日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -818,6 +818,30 @@
   </si>
   <si>
     <t>电力板块走弱了，也超出了自己的盈亏R数了，果断清了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东诚药业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>以为医药是主线，集合竞价就买入了，结果又吃瘪了，看来自己不适合博弈二板的，适合等它回调后再买入。这种情况很容易追高，老是买在高价，有点赌博性质，所以以后不做这样的操作了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金风科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商业航天回流，它还在相对低位，所以就买入了。但是我觉得，我还是比较适合2点半后买入比较合适，因为早上十点半前买入我容易买高位，不好把握。有时自己确实也比较容易冲动，管不住自己的手，还是得改，得再忍忍。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1268,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:T6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1544,6 +1568,80 @@
         <v>104</v>
       </c>
     </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B5" s="16">
+        <v>46112</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2675</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="2">
+        <v>14.978</v>
+      </c>
+      <c r="G5" s="2">
+        <v>700</v>
+      </c>
+      <c r="H5" s="1">
+        <f>E5*G5</f>
+        <v>10484.6</v>
+      </c>
+      <c r="I5" s="1">
+        <f>F5*G5</f>
+        <v>0</v>
+      </c>
+      <c r="M5" s="2">
+        <v>1500</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46112</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2202</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E6" s="2">
+        <v>27.939</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1400</v>
+      </c>
+      <c r="H6" s="2">
+        <f>E6*G6</f>
+        <v>39114.6</v>
+      </c>
+      <c r="I6" s="2">
+        <f>F6*G6</f>
+        <v>0</v>
+      </c>
+      <c r="M6" s="2">
+        <v>1500</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1692,7 +1790,7 @@
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M),"0")</f>
-        <v>-273.0256666666661</v>
+        <v>-260.17739999999947</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>33</v>
@@ -1748,7 +1846,7 @@
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>38</v>
@@ -1760,7 +1858,7 @@
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f>SUMIF(交易记录!F:F,"",交易记录!H:H)</f>
-        <v>67183.199999999997</v>
+        <v>116782.39999999999</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>

--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D55ADDBE-20C6-4709-A434-0E6EBE39D3CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC8D302-0835-406D-BCEE-334357AF9884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="126">
   <si>
     <t>交易日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -90,10 +90,6 @@
   </si>
   <si>
     <t>宝新能源</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>单笔风险1R(元）(按当前账户本金亏损的3%来算)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -805,19 +801,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>算电协同，冲就完事了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>不想持仓了，想空仓一段时间。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电力板块走弱了，也超出了自己的盈亏R数了，果断清了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>东诚药业</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>短线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>算电协同，冲就完事了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>不想持仓了，想空仓一段时间。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>电力板块走弱了，也超出了自己的盈亏R数了，果断清了</t>
+    <t>以为医药是主线，集合竞价就买入了，结果又吃瘪了，看来自己不适合博弈二板的，适合等它回调后再买入。这种情况很容易追高，老是买在高价，有点赌博性质，所以以后不做这样的操作了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>金风科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>商业航天回流，它还在相对低位，所以就买入了。但是我觉得，我还是比较适合2点半后买入比较合适，因为早上十点半前买入我容易买高位，不好把握。有时自己确实也比较容易冲动，管不住自己的手，还是得改，得再忍忍。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -825,7 +841,51 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>东诚药业</t>
+    <t>数据港</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖了，腾仓位买数据港，但貌似又卖飞了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据中心长期逻辑，似乎又买高了，看来不适合上午买票。如果非要上午买票，可以分批次买，先轻仓介入，后续看情况再买。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跌破位了，不指望回本了，为自己的冲动买单。下次不能再这么冲动了。赶着给人家送钱，真想给自己两拳，但还是要稳住心态，心态不能炸，炸了操作就会变形，稳住心态。头脑一热，很容易追涨杀跌。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>单笔风险1R(元）(按当前账户本金亏损的4%来算)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>美利云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中长线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大师兄买入的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被大师兄割肉跑了，买了美利云。我觉得割早了，我本想的是长期持有到18元，目前来看算电协同应该是退朝了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>远东股份</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -833,15 +893,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>以为医药是主线，集合竞价就买入了，结果又吃瘪了，看来自己不适合博弈二板的，适合等它回调后再买入。这种情况很容易追高，老是买在高价，有点赌博性质，所以以后不做这样的操作了。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>金风科技</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>商业航天回流，它还在相对低位，所以就买入了。但是我觉得，我还是比较适合2点半后买入比较合适，因为早上十点半前买入我容易买高位，不好把握。有时自己确实也比较容易冲动，管不住自己的手，还是得改，得再忍忍。</t>
+    <t>多头趋势向上，站稳了5日线</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1292,7 +1344,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T6"/>
+  <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1319,7 +1371,7 @@
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -1331,7 +1383,7 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>3</v>
@@ -1355,7 +1407,7 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>16</v>
+        <v>116</v>
       </c>
       <c r="N1" s="1" t="s">
         <v>9</v>
@@ -1367,7 +1419,7 @@
         <v>12</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>13</v>
@@ -1376,12 +1428,12 @@
         <v>14</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B2" s="16">
         <v>46100</v>
@@ -1390,7 +1442,7 @@
         <v>600498</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E2" s="1">
         <v>43.886000000000003</v>
@@ -1402,11 +1454,11 @@
         <v>600</v>
       </c>
       <c r="H2" s="1">
-        <f>E2*G2</f>
+        <f t="shared" ref="H2:H9" si="0">E2*G2</f>
         <v>26331.600000000002</v>
       </c>
       <c r="I2" s="1">
-        <f>F2*G2</f>
+        <f t="shared" ref="I2:I9" si="1">F2*G2</f>
         <v>28650</v>
       </c>
       <c r="J2" s="1">
@@ -1440,18 +1492,18 @@
         <v>41.323433333333334</v>
       </c>
       <c r="R2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>99</v>
-      </c>
       <c r="T2" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3" s="14">
         <v>46107</v>
@@ -1472,22 +1524,22 @@
         <v>4100</v>
       </c>
       <c r="H3" s="1">
-        <f>E3*G3</f>
+        <f t="shared" si="0"/>
         <v>23788.199999999997</v>
       </c>
       <c r="I3" s="1">
-        <f>F3*G3</f>
+        <f t="shared" si="1"/>
         <v>21033</v>
       </c>
       <c r="J3" s="1">
         <v>7.47</v>
       </c>
       <c r="K3" s="1">
-        <f>IF(F3&lt;&gt;"",I3-H3-J3,"")</f>
+        <f t="shared" ref="K3:K9" si="2">IF(F3&lt;&gt;"",I3-H3-J3,"")</f>
         <v>-2762.6699999999969</v>
       </c>
       <c r="L3" s="11">
-        <f t="shared" ref="L3:L4" si="0">IF(F3&lt;&gt;"",K3/H3*100,"")</f>
+        <f t="shared" ref="L3:L9" si="3">IF(F3&lt;&gt;"",K3/H3*100,"")</f>
         <v>-11.61361515373167</v>
       </c>
       <c r="M3" s="1">
@@ -1510,18 +1562,18 @@
         <v>5.4343243902439013</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="16">
         <v>46108</v>
@@ -1530,47 +1582,68 @@
         <v>1896</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E4" s="2">
         <v>15.624000000000001</v>
       </c>
+      <c r="F4" s="2">
+        <v>12.54</v>
+      </c>
       <c r="G4" s="2">
         <v>4300</v>
       </c>
       <c r="H4" s="1">
-        <f>E4*G4</f>
+        <f t="shared" si="0"/>
         <v>67183.199999999997</v>
       </c>
       <c r="I4" s="1">
-        <f>F4*G4</f>
-        <v>0</v>
-      </c>
-      <c r="K4" s="1" t="str">
-        <f>IF(F4&lt;&gt;"",I4-H4-J4,"")</f>
-        <v/>
-      </c>
-      <c r="L4" s="11" t="str">
-        <f t="shared" si="0"/>
-        <v/>
+        <f t="shared" si="1"/>
+        <v>53921.999999999993</v>
+      </c>
+      <c r="J4" s="2">
+        <v>16.79</v>
+      </c>
+      <c r="K4" s="1">
+        <f t="shared" si="2"/>
+        <v>-13277.990000000005</v>
+      </c>
+      <c r="L4" s="11">
+        <f t="shared" si="3"/>
+        <v>-19.763854654139735</v>
       </c>
       <c r="M4" s="2">
-        <v>2100</v>
+        <v>2800</v>
+      </c>
+      <c r="N4" s="1">
+        <f t="shared" ref="N4:N9" si="4">IF(F4&lt;&gt;"",K4/M4,"")</f>
+        <v>-4.7421392857142877</v>
+      </c>
+      <c r="O4" s="1" t="str">
+        <f t="shared" ref="O4:O9" si="5">IF(F4&lt;&gt;"",IF(K4&gt;0,"盈","亏"),"")</f>
+        <v>亏</v>
+      </c>
+      <c r="P4" s="1">
+        <f t="shared" ref="P4:P9" si="6">IF(F4&lt;&gt;"",IF(K4&gt;0,ABS(K4)/M4,ABS(K4)/M4),"")</f>
+        <v>4.7421392857142877</v>
       </c>
       <c r="Q4" s="1">
         <f>IF(E4&lt;&gt;"",(H4-J4-M4)/G4,"")</f>
-        <v>15.135627906976744</v>
+        <v>14.968932558139535</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+        <v>102</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B5" s="16">
         <v>46112</v>
@@ -1579,35 +1652,68 @@
         <v>2675</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E5" s="2">
         <v>14.978</v>
       </c>
+      <c r="F5" s="2">
+        <v>14.18</v>
+      </c>
       <c r="G5" s="2">
         <v>700</v>
       </c>
       <c r="H5" s="1">
-        <f>E5*G5</f>
+        <f t="shared" si="0"/>
         <v>10484.6</v>
       </c>
       <c r="I5" s="1">
-        <f>F5*G5</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>9926</v>
+      </c>
+      <c r="J5" s="2">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="K5" s="1">
+        <f t="shared" si="2"/>
+        <v>-563.70000000000039</v>
+      </c>
+      <c r="L5" s="11">
+        <f>IF(F5&lt;&gt;"",K5/H5*100,"")</f>
+        <v>-5.3764568986895096</v>
       </c>
       <c r="M5" s="2">
         <v>1500</v>
       </c>
+      <c r="N5" s="1">
+        <f t="shared" si="4"/>
+        <v>-0.37580000000000024</v>
+      </c>
+      <c r="O5" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>亏</v>
+      </c>
+      <c r="P5" s="1">
+        <f t="shared" si="6"/>
+        <v>0.37580000000000024</v>
+      </c>
+      <c r="Q5" s="1">
+        <f t="shared" ref="Q5:Q9" si="7">IF(E5&lt;&gt;"",(H5-J5-M5)/G5,"")</f>
+        <v>12.827857142857143</v>
+      </c>
       <c r="R5" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B6" s="16">
         <v>46112</v>
@@ -1616,30 +1722,252 @@
         <v>2202</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E6" s="2">
         <v>27.939</v>
       </c>
+      <c r="F6" s="2">
+        <v>25.35</v>
+      </c>
       <c r="G6" s="2">
         <v>1400</v>
       </c>
       <c r="H6" s="2">
-        <f>E6*G6</f>
+        <f t="shared" si="0"/>
         <v>39114.6</v>
       </c>
       <c r="I6" s="2">
-        <f>F6*G6</f>
-        <v>0</v>
+        <f t="shared" si="1"/>
+        <v>35490</v>
+      </c>
+      <c r="J6" s="2">
+        <v>12.3</v>
+      </c>
+      <c r="K6" s="1">
+        <f t="shared" si="2"/>
+        <v>-3636.8999999999987</v>
+      </c>
+      <c r="L6" s="11">
+        <f t="shared" si="3"/>
+        <v>-9.2980626160052751</v>
       </c>
       <c r="M6" s="2">
         <v>1500</v>
       </c>
+      <c r="N6" s="1">
+        <f t="shared" si="4"/>
+        <v>-2.424599999999999</v>
+      </c>
+      <c r="O6" s="1" t="str">
+        <f t="shared" si="5"/>
+        <v>亏</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="6"/>
+        <v>2.424599999999999</v>
+      </c>
+      <c r="Q6" s="1">
+        <f t="shared" si="7"/>
+        <v>26.858785714285712</v>
+      </c>
       <c r="R6" s="2" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="S6" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B7" s="16">
+        <v>46113</v>
+      </c>
+      <c r="C7" s="2">
+        <v>603881</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>37.996000000000002</v>
+      </c>
+      <c r="F7" s="2">
+        <v>39.409999999999997</v>
+      </c>
+      <c r="G7" s="2">
+        <v>1100</v>
+      </c>
+      <c r="H7" s="2">
+        <f t="shared" si="0"/>
+        <v>41795.600000000006</v>
+      </c>
+      <c r="I7" s="2">
+        <f t="shared" si="1"/>
+        <v>43350.999999999993</v>
+      </c>
+      <c r="J7" s="2">
+        <v>55.43</v>
+      </c>
+      <c r="K7" s="2">
+        <f t="shared" si="2"/>
+        <v>1499.9699999999868</v>
+      </c>
+      <c r="L7" s="11">
+        <f t="shared" si="3"/>
+        <v>3.5888227468919855</v>
+      </c>
+      <c r="M7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="N7" s="1">
+        <f t="shared" si="4"/>
+        <v>0.74998499999999346</v>
+      </c>
+      <c r="O7" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>盈</v>
+      </c>
+      <c r="P7" s="2">
+        <f t="shared" si="6"/>
+        <v>0.74998499999999346</v>
+      </c>
+      <c r="Q7" s="2">
+        <f t="shared" si="7"/>
+        <v>36.127427272727274</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8" s="16">
+        <v>46115</v>
+      </c>
+      <c r="C8" s="2">
+        <v>815</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E8" s="2">
+        <v>19.638999999999999</v>
+      </c>
+      <c r="G8" s="2">
+        <v>2700</v>
+      </c>
+      <c r="H8" s="2">
+        <f t="shared" si="0"/>
+        <v>53025.299999999996</v>
+      </c>
+      <c r="I8" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L8" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="N8" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O8" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P8" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" si="7"/>
+        <v>18.898259259259259</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B9" s="16">
+        <v>46122</v>
+      </c>
+      <c r="C9" s="2">
+        <v>600869</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E9" s="2">
+        <v>15.871</v>
+      </c>
+      <c r="G9" s="2">
+        <v>2900</v>
+      </c>
+      <c r="H9" s="2">
+        <f t="shared" si="0"/>
+        <v>46025.9</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K9" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="L9" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="M9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="N9" s="2" t="str">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="O9" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="P9" s="2" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" si="7"/>
+        <v>15.181344827586207</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -1661,154 +1989,154 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <f>COUNTIF(交易记录!O:O,"盈")+COUNTIF(交易记录!O:O,"亏")</f>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <f>COUNTIF(交易记录!O:O,"盈")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <f>COUNTIF(交易记录!O:O,"亏")</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(A2&gt;0,A3/A2*100,"0")</f>
-        <v>50</v>
+        <v>33.333333333333329</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <f>SUM(交易记录!K:K)</f>
-        <v>-481.80999999999904</v>
+        <v>-16460.430000000018</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <f>IF(A2&gt;0,A6/A2,"0")</f>
-        <v>-240.90499999999952</v>
+        <v>-2743.4050000000029</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <f>IF(A3&gt;0,AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
-        <v>1.520573333333332</v>
+        <v>1.1352791666666628</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f>IF(A4&gt;0,ABS(AVERAGEIF(交易记录!N:N,"&lt;0",交易记录!N:N)),"0")</f>
-        <v>1.841779999999998</v>
+        <v>2.346079821428571</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <f>IF(A9&gt;0,A8/A9,"0")</f>
-        <v>0.8255998725870265</v>
+        <v>0.4839047488057634</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f>IF(A2&gt;0,(A5/100)*A8 - (1-A5/100)*A9,"0")</f>
-        <v>-0.16060333333333299</v>
+        <v>-1.1856268253968267</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M),"0")</f>
-        <v>-260.17739999999947</v>
+        <v>-2193.4096269841293</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <f>SUM(交易记录!N:N)</f>
-        <v>-0.32120666666666597</v>
+        <v>-7.1137609523809591</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
@@ -1817,54 +2145,54 @@
         <v>1</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <f t="array" ref="A15">MAX(FREQUENCY(IF(交易记录!O:O="亏",ROW(交易记录!O:O)),IF(交易记录!O:O&lt;&gt;"亏",ROW(交易记录!O:O))))</f>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f>SUMIF(交易记录!F:F,"",交易记录!H:H)</f>
-        <v>116782.39999999999</v>
+        <v>99051.199999999997</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1891,54 +2219,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" t="s">
         <v>71</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="11" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>64</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -1958,7 +2286,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F3" s="10" t="e">
         <f>IF(E3&gt;0,E3/50000*100,"0")</f>
@@ -1990,7 +2318,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F4" s="10" t="e">
         <f t="shared" ref="F4:F14" si="1">IF(E4&gt;0,E4/50000*100,"0")</f>
@@ -2022,7 +2350,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F5" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2054,7 +2382,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F6" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2086,7 +2414,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F7" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2118,7 +2446,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2150,7 +2478,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F9" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2182,7 +2510,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F10" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2214,7 +2542,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F11" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2246,7 +2574,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F12" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2278,7 +2606,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F13" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2310,7 +2638,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F14" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2345,12 +2673,12 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B2">
         <v>70000</v>
@@ -2358,7 +2686,7 @@
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B3">
         <v>2100</v>
@@ -2366,24 +2694,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>92</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">

--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FC8D302-0835-406D-BCEE-334357AF9884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26E5F08-4AC5-4AD5-8A0A-14657317B72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,11 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="126">
-  <si>
-    <t>交易日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="135">
   <si>
     <t>股票代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -861,23 +857,63 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>美利云</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中长线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>大师兄买入的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>被大师兄割肉跑了，买了美利云。我觉得割早了，我本想的是长期持有到18元，目前来看算电协同应该是退朝了。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>国信</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>美利云</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>中长线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>大师兄买入的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>被大师兄割肉跑了，买了美利云。我觉得割早了，我本想的是长期持有到18元，目前来看算电协同应该是退朝了。</t>
+    <t>远东股份</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>多头趋势向上，站稳了5日线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>中信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>破位了14.2，卖太急了，条件单还是不要顺便乱设置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没握住，卖完第二天就涨停了。不过卖飞总比亏损强</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>国机精工</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>买入日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>卖出日期</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -885,15 +921,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>远东股份</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>短线</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>多头趋势向上，站稳了5日线</t>
+    <t>云赛智联</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>趋势向上，但是买点似乎不是很好</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没看出很强，不懂里面逻辑，业绩估计也不是很好，所以清了</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1344,630 +1380,791 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T9"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
-    <col min="2" max="2" width="16.125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="15.75" style="2" customWidth="1"/>
-    <col min="4" max="4" width="17" style="2" customWidth="1"/>
-    <col min="5" max="5" width="23.25" style="2" customWidth="1"/>
-    <col min="6" max="6" width="18.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.25" style="2" customWidth="1"/>
-    <col min="8" max="8" width="17.625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="17.25" style="2" customWidth="1"/>
-    <col min="10" max="10" width="11.375" style="2" customWidth="1"/>
-    <col min="11" max="11" width="22.625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="15" style="2" customWidth="1"/>
-    <col min="13" max="13" width="17.25" style="2" customWidth="1"/>
-    <col min="14" max="14" width="19.875" style="2" customWidth="1"/>
-    <col min="15" max="15" width="9" style="2"/>
-    <col min="16" max="17" width="15.5" style="2" customWidth="1"/>
-    <col min="18" max="18" width="13.625" style="2" customWidth="1"/>
-    <col min="19" max="19" width="18.625" style="2" customWidth="1"/>
-    <col min="20" max="20" width="16.875" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="2"/>
+    <col min="2" max="3" width="16.125" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.75" style="2" customWidth="1"/>
+    <col min="5" max="5" width="17" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.25" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="2" customWidth="1"/>
+    <col min="9" max="9" width="17.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="2" customWidth="1"/>
+    <col min="11" max="11" width="11.375" style="2" customWidth="1"/>
+    <col min="12" max="12" width="22.625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="15" style="2" customWidth="1"/>
+    <col min="14" max="14" width="17.25" style="2" customWidth="1"/>
+    <col min="15" max="15" width="19.875" style="2" customWidth="1"/>
+    <col min="16" max="16" width="9" style="2"/>
+    <col min="17" max="18" width="15.5" style="2" customWidth="1"/>
+    <col min="19" max="19" width="13.625" style="2" customWidth="1"/>
+    <col min="20" max="20" width="18.625" style="2" customWidth="1"/>
+    <col min="21" max="21" width="16.875" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="R1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="S1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="T1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="15" x14ac:dyDescent="0.2">
+      <c r="A2" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="S1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="T1" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20" ht="15" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="B2" s="16">
         <v>46100</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="16">
+        <v>46111</v>
+      </c>
+      <c r="D2" s="2">
         <v>600498</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="1">
+        <v>43.886000000000003</v>
+      </c>
+      <c r="G2" s="1">
+        <v>47.75</v>
+      </c>
+      <c r="H2" s="1">
+        <v>600</v>
+      </c>
+      <c r="I2" s="1">
+        <f t="shared" ref="I2:I11" si="0">F2*H2</f>
+        <v>26331.600000000002</v>
+      </c>
+      <c r="J2" s="1">
+        <f t="shared" ref="J2:J10" si="1">G2*H2</f>
+        <v>28650</v>
+      </c>
+      <c r="K2" s="1">
+        <v>37.54</v>
+      </c>
+      <c r="L2" s="1">
+        <f>IF(G2&lt;&gt;"",J2-I2-K2,"")</f>
+        <v>2280.8599999999979</v>
+      </c>
+      <c r="M2" s="11">
+        <f>IF(G2&lt;&gt;"",L2/I2*100,"")</f>
+        <v>8.6620638320496965</v>
+      </c>
+      <c r="N2" s="1">
+        <v>1500</v>
+      </c>
+      <c r="O2" s="1">
+        <f>IF(G2&lt;&gt;"",L2/N2,"")</f>
+        <v>1.520573333333332</v>
+      </c>
+      <c r="P2" s="1" t="str">
+        <f>IF(G2&lt;&gt;"",IF(L2&gt;0,"盈","亏"),"")</f>
+        <v>盈</v>
+      </c>
+      <c r="Q2" s="1">
+        <f>IF(G2&lt;&gt;"",IF(L2&gt;0,ABS(L2)/N2,ABS(L2)/N2),"")</f>
+        <v>1.520573333333332</v>
+      </c>
+      <c r="R2" s="1">
+        <f>IF(F2&lt;&gt;"",(I2-K2-N2)/H2,"")</f>
+        <v>41.323433333333334</v>
+      </c>
+      <c r="S2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="1">
-        <v>43.886000000000003</v>
-      </c>
-      <c r="F2" s="1">
-        <v>47.75</v>
-      </c>
-      <c r="G2" s="1">
-        <v>600</v>
-      </c>
-      <c r="H2" s="1">
-        <f t="shared" ref="H2:H9" si="0">E2*G2</f>
-        <v>26331.600000000002</v>
-      </c>
-      <c r="I2" s="1">
-        <f t="shared" ref="I2:I9" si="1">F2*G2</f>
-        <v>28650</v>
-      </c>
-      <c r="J2" s="1">
-        <v>37.54</v>
-      </c>
-      <c r="K2" s="1">
-        <f>IF(F2&lt;&gt;"",I2-H2-J2,"")</f>
-        <v>2280.8599999999979</v>
-      </c>
-      <c r="L2" s="11">
-        <f>IF(F2&lt;&gt;"",K2/H2*100,"")</f>
-        <v>8.6620638320496965</v>
-      </c>
-      <c r="M2" s="1">
-        <v>1500</v>
-      </c>
-      <c r="N2" s="1">
-        <f>IF(F2&lt;&gt;"",K2/M2,"")</f>
-        <v>1.520573333333332</v>
-      </c>
-      <c r="O2" s="1" t="str">
-        <f>IF(F2&lt;&gt;"",IF(K2&gt;0,"盈","亏"),"")</f>
-        <v>盈</v>
-      </c>
-      <c r="P2" s="1">
-        <f>IF(F2&lt;&gt;"",IF(K2&gt;0,ABS(K2)/M2,ABS(K2)/M2),"")</f>
-        <v>1.520573333333332</v>
-      </c>
-      <c r="Q2" s="1">
-        <f>IF(E2&lt;&gt;"",(H2-J2-M2)/G2,"")</f>
-        <v>41.323433333333334</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="T2" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="S2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="U2" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B3" s="14">
         <v>46107</v>
       </c>
-      <c r="C3" s="1">
+      <c r="C3" s="14">
+        <v>46111</v>
+      </c>
+      <c r="D3" s="1">
         <v>690</v>
       </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1">
+      <c r="E3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="1">
         <v>5.8019999999999996</v>
       </c>
-      <c r="F3" s="1">
+      <c r="G3" s="1">
         <v>5.13</v>
       </c>
-      <c r="G3" s="1">
+      <c r="H3" s="1">
         <v>4100</v>
       </c>
-      <c r="H3" s="1">
+      <c r="I3" s="1">
         <f t="shared" si="0"/>
         <v>23788.199999999997</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3" s="1">
         <f t="shared" si="1"/>
         <v>21033</v>
       </c>
-      <c r="J3" s="1">
+      <c r="K3" s="1">
         <v>7.47</v>
       </c>
-      <c r="K3" s="1">
-        <f t="shared" ref="K3:K9" si="2">IF(F3&lt;&gt;"",I3-H3-J3,"")</f>
+      <c r="L3" s="1">
+        <f t="shared" ref="L3:L11" si="2">IF(G3&lt;&gt;"",J3-I3-K3,"")</f>
         <v>-2762.6699999999969</v>
       </c>
-      <c r="L3" s="11">
-        <f t="shared" ref="L3:L9" si="3">IF(F3&lt;&gt;"",K3/H3*100,"")</f>
+      <c r="M3" s="11">
+        <f t="shared" ref="M3:M11" si="3">IF(G3&lt;&gt;"",L3/I3*100,"")</f>
         <v>-11.61361515373167</v>
       </c>
-      <c r="M3" s="1">
+      <c r="N3" s="1">
         <v>1500</v>
       </c>
-      <c r="N3" s="1">
-        <f>IF(F3&lt;&gt;"",K3/M3,"")</f>
+      <c r="O3" s="1">
+        <f>IF(G3&lt;&gt;"",L3/N3,"")</f>
         <v>-1.841779999999998</v>
       </c>
-      <c r="O3" s="1" t="str">
-        <f>IF(F3&lt;&gt;"",IF(K3&gt;0,"盈","亏"),"")</f>
+      <c r="P3" s="1" t="str">
+        <f>IF(G3&lt;&gt;"",IF(L3&gt;0,"盈","亏"),"")</f>
         <v>亏</v>
       </c>
-      <c r="P3" s="1">
-        <f>IF(F3&lt;&gt;"",IF(K3&gt;0,ABS(K3)/M3,ABS(K3)/M3),"")</f>
+      <c r="Q3" s="1">
+        <f>IF(G3&lt;&gt;"",IF(L3&gt;0,ABS(L3)/N3,ABS(L3)/N3),"")</f>
         <v>1.841779999999998</v>
       </c>
-      <c r="Q3" s="1">
-        <f>IF(E3&lt;&gt;"",(H3-J3-M3)/G3,"")</f>
+      <c r="R3" s="1">
+        <f>IF(F3&lt;&gt;"",(I3-K3-N3)/H3,"")</f>
         <v>5.4343243902439013</v>
       </c>
-      <c r="R3" s="1" t="s">
-        <v>16</v>
-      </c>
       <c r="S3" s="1" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B4" s="16">
         <v>46108</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="16">
+        <v>46115</v>
+      </c>
+      <c r="D4" s="2">
         <v>1896</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E4" s="2">
+      <c r="E4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F4" s="2">
         <v>15.624000000000001</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>12.54</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>4300</v>
       </c>
-      <c r="H4" s="1">
+      <c r="I4" s="1">
         <f t="shared" si="0"/>
         <v>67183.199999999997</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4" s="1">
         <f t="shared" si="1"/>
         <v>53921.999999999993</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>16.79</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <f t="shared" si="2"/>
         <v>-13277.990000000005</v>
       </c>
-      <c r="L4" s="11">
+      <c r="M4" s="11">
         <f t="shared" si="3"/>
         <v>-19.763854654139735</v>
       </c>
-      <c r="M4" s="2">
+      <c r="N4" s="2">
         <v>2800</v>
       </c>
-      <c r="N4" s="1">
-        <f t="shared" ref="N4:N9" si="4">IF(F4&lt;&gt;"",K4/M4,"")</f>
+      <c r="O4" s="1">
+        <f t="shared" ref="O4:O10" si="4">IF(G4&lt;&gt;"",L4/N4,"")</f>
         <v>-4.7421392857142877</v>
       </c>
-      <c r="O4" s="1" t="str">
-        <f t="shared" ref="O4:O9" si="5">IF(F4&lt;&gt;"",IF(K4&gt;0,"盈","亏"),"")</f>
+      <c r="P4" s="1" t="str">
+        <f t="shared" ref="P4:P11" si="5">IF(G4&lt;&gt;"",IF(L4&gt;0,"盈","亏"),"")</f>
         <v>亏</v>
       </c>
-      <c r="P4" s="1">
-        <f t="shared" ref="P4:P9" si="6">IF(F4&lt;&gt;"",IF(K4&gt;0,ABS(K4)/M4,ABS(K4)/M4),"")</f>
+      <c r="Q4" s="1">
+        <f t="shared" ref="Q4:Q10" si="6">IF(G4&lt;&gt;"",IF(L4&gt;0,ABS(L4)/N4,ABS(L4)/N4),"")</f>
         <v>4.7421392857142877</v>
       </c>
-      <c r="Q4" s="1">
-        <f>IF(E4&lt;&gt;"",(H4-J4-M4)/G4,"")</f>
+      <c r="R4" s="1">
+        <f>IF(F4&lt;&gt;"",(I4-K4-N4)/H4,"")</f>
         <v>14.968932558139535</v>
       </c>
-      <c r="R4" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="S4" s="2" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" ht="15" x14ac:dyDescent="0.2">
+        <v>101</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B5" s="16">
         <v>46112</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="16">
+        <v>46113</v>
+      </c>
+      <c r="D5" s="2">
         <v>2675</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E5" s="2">
+      <c r="E5" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="2">
         <v>14.978</v>
       </c>
-      <c r="F5" s="2">
+      <c r="G5" s="2">
         <v>14.18</v>
       </c>
-      <c r="G5" s="2">
+      <c r="H5" s="2">
         <v>700</v>
       </c>
-      <c r="H5" s="1">
+      <c r="I5" s="1">
         <f t="shared" si="0"/>
         <v>10484.6</v>
       </c>
-      <c r="I5" s="1">
+      <c r="J5" s="1">
         <f t="shared" si="1"/>
         <v>9926</v>
       </c>
-      <c r="J5" s="2">
+      <c r="K5" s="2">
         <v>5.0999999999999996</v>
       </c>
-      <c r="K5" s="1">
+      <c r="L5" s="1">
         <f t="shared" si="2"/>
         <v>-563.70000000000039</v>
       </c>
-      <c r="L5" s="11">
-        <f>IF(F5&lt;&gt;"",K5/H5*100,"")</f>
+      <c r="M5" s="11">
+        <f>IF(G5&lt;&gt;"",L5/I5*100,"")</f>
         <v>-5.3764568986895096</v>
       </c>
-      <c r="M5" s="2">
+      <c r="N5" s="2">
         <v>1500</v>
       </c>
-      <c r="N5" s="1">
+      <c r="O5" s="1">
         <f t="shared" si="4"/>
         <v>-0.37580000000000024</v>
       </c>
-      <c r="O5" s="1" t="str">
+      <c r="P5" s="1" t="str">
         <f t="shared" si="5"/>
         <v>亏</v>
       </c>
-      <c r="P5" s="1">
+      <c r="Q5" s="1">
         <f t="shared" si="6"/>
         <v>0.37580000000000024</v>
       </c>
-      <c r="Q5" s="1">
-        <f t="shared" ref="Q5:Q9" si="7">IF(E5&lt;&gt;"",(H5-J5-M5)/G5,"")</f>
+      <c r="R5" s="1">
+        <f t="shared" ref="R5:R11" si="7">IF(F5&lt;&gt;"",(I5-K5-N5)/H5,"")</f>
         <v>12.827857142857143</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T5" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="U5" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="16">
         <v>46112</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="16">
+        <v>46113</v>
+      </c>
+      <c r="D6" s="2">
         <v>2202</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="E6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F6" s="2">
         <v>27.939</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>25.35</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>1400</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <f t="shared" si="0"/>
         <v>39114.6</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <f t="shared" si="1"/>
         <v>35490</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>12.3</v>
       </c>
-      <c r="K6" s="1">
+      <c r="L6" s="1">
         <f t="shared" si="2"/>
         <v>-3636.8999999999987</v>
       </c>
-      <c r="L6" s="11">
+      <c r="M6" s="11">
         <f t="shared" si="3"/>
         <v>-9.2980626160052751</v>
       </c>
-      <c r="M6" s="2">
+      <c r="N6" s="2">
         <v>1500</v>
       </c>
-      <c r="N6" s="1">
+      <c r="O6" s="1">
         <f t="shared" si="4"/>
         <v>-2.424599999999999</v>
       </c>
-      <c r="O6" s="1" t="str">
+      <c r="P6" s="1" t="str">
         <f t="shared" si="5"/>
         <v>亏</v>
       </c>
-      <c r="P6" s="1">
+      <c r="Q6" s="1">
         <f t="shared" si="6"/>
         <v>2.424599999999999</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="R6" s="1">
         <f t="shared" si="7"/>
         <v>26.858785714285712</v>
       </c>
-      <c r="R6" s="2" t="s">
-        <v>107</v>
-      </c>
       <c r="S6" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="15" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
         <v>110</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" ht="15" x14ac:dyDescent="0.2">
-      <c r="A7" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="B7" s="16">
         <v>46113</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="16">
+        <v>46122</v>
+      </c>
+      <c r="D7" s="2">
         <v>603881</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="2">
+      <c r="E7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="F7" s="2">
         <v>37.996000000000002</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>39.409999999999997</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>1100</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <f t="shared" si="0"/>
         <v>41795.600000000006</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <f t="shared" si="1"/>
         <v>43350.999999999993</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>55.43</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <f t="shared" si="2"/>
         <v>1499.9699999999868</v>
       </c>
-      <c r="L7" s="11">
+      <c r="M7" s="11">
         <f t="shared" si="3"/>
         <v>3.5888227468919855</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>2000</v>
       </c>
-      <c r="N7" s="1">
+      <c r="O7" s="1">
         <f t="shared" si="4"/>
         <v>0.74998499999999346</v>
       </c>
-      <c r="O7" s="2" t="str">
+      <c r="P7" s="2" t="str">
         <f t="shared" si="5"/>
         <v>盈</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <f t="shared" si="6"/>
         <v>0.74998499999999346</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <f t="shared" si="7"/>
         <v>36.127427272727274</v>
       </c>
-      <c r="R7" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="S7" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="B8" s="16">
         <v>46115</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8" s="16">
+        <v>46127</v>
+      </c>
+      <c r="D8" s="2">
         <v>815</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E8" s="2">
+      <c r="E8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F8" s="2">
         <v>19.638999999999999</v>
       </c>
       <c r="G8" s="2">
+        <v>20.75</v>
+      </c>
+      <c r="H8" s="2">
         <v>2700</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <f t="shared" si="0"/>
         <v>53025.299999999996</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K8" s="2" t="str">
+        <v>56025</v>
+      </c>
+      <c r="K8" s="2">
+        <v>91.24</v>
+      </c>
+      <c r="L8" s="2">
+        <f t="shared" si="2"/>
+        <v>2908.4600000000046</v>
+      </c>
+      <c r="M8" s="2">
+        <f t="shared" si="3"/>
+        <v>5.4850420459667451</v>
+      </c>
+      <c r="N8" s="2">
+        <v>2000</v>
+      </c>
+      <c r="O8" s="2">
+        <f t="shared" si="4"/>
+        <v>1.4542300000000024</v>
+      </c>
+      <c r="P8" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>盈</v>
+      </c>
+      <c r="Q8" s="2">
+        <f t="shared" si="6"/>
+        <v>1.4542300000000024</v>
+      </c>
+      <c r="R8" s="2">
+        <f t="shared" si="7"/>
+        <v>18.864466666666665</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B9" s="16">
+        <v>46122</v>
+      </c>
+      <c r="C9" s="16">
+        <v>46128</v>
+      </c>
+      <c r="D9" s="2">
+        <v>600869</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F9" s="2">
+        <v>15.871</v>
+      </c>
+      <c r="G9" s="2">
+        <v>14.07</v>
+      </c>
+      <c r="H9" s="2">
+        <v>2900</v>
+      </c>
+      <c r="I9" s="2">
+        <f t="shared" si="0"/>
+        <v>46025.9</v>
+      </c>
+      <c r="J9" s="2">
+        <f t="shared" si="1"/>
+        <v>40803</v>
+      </c>
+      <c r="K9" s="2">
+        <v>14.46</v>
+      </c>
+      <c r="L9" s="2">
+        <f t="shared" si="2"/>
+        <v>-5237.3600000000015</v>
+      </c>
+      <c r="M9" s="2">
+        <f t="shared" si="3"/>
+        <v>-11.379158256546861</v>
+      </c>
+      <c r="N9" s="2">
+        <v>2000</v>
+      </c>
+      <c r="O9" s="2">
+        <f t="shared" si="4"/>
+        <v>-2.6186800000000008</v>
+      </c>
+      <c r="P9" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>亏</v>
+      </c>
+      <c r="Q9" s="2">
+        <f t="shared" si="6"/>
+        <v>2.6186800000000008</v>
+      </c>
+      <c r="R9" s="2">
+        <f t="shared" si="7"/>
+        <v>15.176358620689657</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B10" s="16">
+        <v>46127</v>
+      </c>
+      <c r="C10" s="16">
+        <v>46129</v>
+      </c>
+      <c r="D10" s="2">
+        <v>2046</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F10" s="2">
+        <v>49.512</v>
+      </c>
+      <c r="G10" s="2">
+        <v>50.05</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1000</v>
+      </c>
+      <c r="I10" s="2">
+        <f t="shared" si="0"/>
+        <v>49512</v>
+      </c>
+      <c r="J10" s="2">
+        <f t="shared" si="1"/>
+        <v>50050</v>
+      </c>
+      <c r="K10" s="2">
+        <v>12.38</v>
+      </c>
+      <c r="L10" s="2">
+        <f t="shared" si="2"/>
+        <v>525.62</v>
+      </c>
+      <c r="M10" s="2">
+        <f t="shared" si="3"/>
+        <v>1.061601227985135</v>
+      </c>
+      <c r="N10" s="2">
+        <v>2400</v>
+      </c>
+      <c r="O10" s="2">
+        <f t="shared" si="4"/>
+        <v>0.21900833333333333</v>
+      </c>
+      <c r="P10" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v>盈</v>
+      </c>
+      <c r="Q10" s="2">
+        <f t="shared" si="6"/>
+        <v>0.21900833333333333</v>
+      </c>
+      <c r="R10" s="2">
+        <f t="shared" si="7"/>
+        <v>47.099620000000002</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="B11" s="16">
+        <v>46128</v>
+      </c>
+      <c r="D11" s="2">
+        <v>600602</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11" s="2">
+        <v>24.651</v>
+      </c>
+      <c r="H11" s="2">
+        <v>800</v>
+      </c>
+      <c r="I11" s="2">
+        <f t="shared" si="0"/>
+        <v>19720.8</v>
+      </c>
+      <c r="L11" s="2" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
-      <c r="L8" s="2" t="str">
+      <c r="M11" s="2" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
-      <c r="M8" s="2">
+      <c r="N11" s="2">
         <v>2000</v>
       </c>
-      <c r="N8" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="O8" s="2" t="str">
+      <c r="P11" s="2" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="P8" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Q8" s="2">
+      <c r="R11" s="2">
         <f t="shared" si="7"/>
-        <v>18.898259259259259</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
-      <c r="A9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="B9" s="16">
-        <v>46122</v>
-      </c>
-      <c r="C9" s="2">
-        <v>600869</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="E9" s="2">
-        <v>15.871</v>
-      </c>
-      <c r="G9" s="2">
-        <v>2900</v>
-      </c>
-      <c r="H9" s="2">
-        <f t="shared" si="0"/>
-        <v>46025.9</v>
-      </c>
-      <c r="I9" s="2">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="L9" s="2" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-      <c r="M9" s="2">
-        <v>2000</v>
-      </c>
-      <c r="N9" s="2" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-      <c r="O9" s="2" t="str">
-        <f t="shared" si="5"/>
-        <v/>
-      </c>
-      <c r="P9" s="2" t="str">
-        <f t="shared" si="6"/>
-        <v/>
-      </c>
-      <c r="Q9" s="2">
-        <f t="shared" si="7"/>
-        <v>15.181344827586207</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>125</v>
+        <v>22.151</v>
       </c>
     </row>
   </sheetData>
@@ -1989,215 +2186,216 @@
   <sheetData>
     <row r="1" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
-        <f>COUNTIF(交易记录!O:O,"盈")+COUNTIF(交易记录!O:O,"亏")</f>
-        <v>6</v>
+        <f>COUNTIF(交易记录!P:P,"盈")+COUNTIF(交易记录!P:P,"亏")</f>
+        <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <f>COUNTIF(交易记录!O:O,"盈")</f>
-        <v>2</v>
+        <f>COUNTIF(交易记录!P:P,"盈")</f>
+        <v>4</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
-        <f>COUNTIF(交易记录!O:O,"亏")</f>
-        <v>4</v>
+        <f>COUNTIF(交易记录!P:P,"亏")</f>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(A2&gt;0,A3/A2*100,"0")</f>
-        <v>33.333333333333329</v>
+        <v>44.444444444444443</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
-        <f>SUM(交易记录!K:K)</f>
-        <v>-16460.430000000018</v>
+        <f>SUM(交易记录!L:L)</f>
+        <v>-18263.710000000017</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <f>IF(A2&gt;0,A6/A2,"0")</f>
-        <v>-2743.4050000000029</v>
+        <v>-2029.301111111113</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <f>IF(A3&gt;0,AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
-        <v>1.1352791666666628</v>
+        <f>IF(A3&gt;0,AVERAGEIF(交易记录!O:O,"&gt;0",交易记录!O:O),"0")</f>
+        <v>0.98594916666666543</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <f>IF(A4&gt;0,ABS(AVERAGEIF(交易记录!N:N,"&lt;0",交易记录!N:N)),"0")</f>
-        <v>2.346079821428571</v>
+        <f>IF(A4&gt;0,ABS(AVERAGEIF(交易记录!O:O,"&lt;0",交易记录!O:O)),"0")</f>
+        <v>2.4005998571428568</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <f>IF(A9&gt;0,A8/A9,"0")</f>
-        <v>0.4839047488057634</v>
+        <v>0.41070949984980892</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f>IF(A2&gt;0,(A5/100)*A8 - (1-A5/100)*A9,"0")</f>
-        <v>-1.1856268253968267</v>
+        <v>-0.89546695767195805</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!M:M,"&gt;0",交易记录!M:M),"0")</f>
-        <v>-2193.4096269841293</v>
+        <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
+        <v>-1719.2965587301594</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
-        <f>SUM(交易记录!N:N)</f>
-        <v>-7.1137609523809591</v>
+        <f>SUM(交易记录!O:O)</f>
+        <v>-8.0592026190476247</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
-        <f t="array" ref="A14">MAX(FREQUENCY(IF(交易记录!O:O="盈",ROW(交易记录!O:O)),IF(交易记录!O:O&lt;&gt;"盈",ROW(交易记录!O:O))))</f>
-        <v>1</v>
+        <f t="array" ref="A14">MAX(FREQUENCY(IF(交易记录!P:P="盈",ROW(交易记录!P:P)),IF(交易记录!P:P&lt;&gt;"盈",ROW(交易记录!P:P))))</f>
+        <v>2</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
-        <f t="array" ref="A15">MAX(FREQUENCY(IF(交易记录!O:O="亏",ROW(交易记录!O:O)),IF(交易记录!O:O&lt;&gt;"亏",ROW(交易记录!O:O))))</f>
+        <f t="array" ref="A15">MAX(FREQUENCY(IF(交易记录!P:P="亏",ROW(交易记录!P:P)),IF(交易记录!P:P&lt;&gt;"亏",ROW(交易记录!P:P))))</f>
         <v>4</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
-        <f>SUMIF(交易记录!F:F,"",交易记录!H:H)</f>
-        <v>99051.199999999997</v>
+        <f>SUMIF(交易记录!G:G,"",交易记录!I:I)</f>
+        <v>19720.8</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2219,54 +2417,54 @@
   <sheetData>
     <row r="1" spans="1:8" ht="30.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="E1" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>72</v>
-      </c>
-      <c r="H1" s="11" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="C2" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="D2" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="F2" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="G2" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="H2" s="9" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
@@ -2274,11 +2472,11 @@
         <v>1</v>
       </c>
       <c r="B3" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A3)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A3)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C3" s="11" t="e">
-        <f t="array" ref="C3">SUMPRODUCT((MONTH(交易记录!B:B)=A3)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C3">SUMPRODUCT((MONTH(交易记录!B:B)=A3)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D3" s="11" t="e">
@@ -2286,7 +2484,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F3" s="10" t="e">
         <f>IF(E3&gt;0,E3/50000*100,"0")</f>
@@ -2306,11 +2504,11 @@
         <v>2</v>
       </c>
       <c r="B4" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A4)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A4)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C4" s="11" t="e">
-        <f t="array" ref="C4">SUMPRODUCT((MONTH(交易记录!B:B)=A4)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C4">SUMPRODUCT((MONTH(交易记录!B:B)=A4)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D4" s="11" t="e">
@@ -2318,7 +2516,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="10" t="e">
         <f t="shared" ref="F4:F14" si="1">IF(E4&gt;0,E4/50000*100,"0")</f>
@@ -2338,11 +2536,11 @@
         <v>3</v>
       </c>
       <c r="B5" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A5)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A5)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C5" s="11" t="e">
-        <f t="array" ref="C5">SUMPRODUCT((MONTH(交易记录!B:B)=A5)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C5">SUMPRODUCT((MONTH(交易记录!B:B)=A5)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D5" s="11" t="e">
@@ -2350,7 +2548,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F5" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2370,11 +2568,11 @@
         <v>4</v>
       </c>
       <c r="B6" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A6)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A6)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C6" s="11" t="e">
-        <f t="array" ref="C6">SUMPRODUCT((MONTH(交易记录!B:B)=A6)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C6">SUMPRODUCT((MONTH(交易记录!B:B)=A6)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D6" s="11" t="e">
@@ -2382,7 +2580,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F6" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2402,11 +2600,11 @@
         <v>5</v>
       </c>
       <c r="B7" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A7)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A7)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C7" s="11" t="e">
-        <f t="array" ref="C7">SUMPRODUCT((MONTH(交易记录!B:B)=A7)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C7">SUMPRODUCT((MONTH(交易记录!B:B)=A7)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D7" s="11" t="e">
@@ -2414,7 +2612,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F7" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2434,11 +2632,11 @@
         <v>6</v>
       </c>
       <c r="B8" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A8)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A8)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C8" s="11" t="e">
-        <f t="array" ref="C8">SUMPRODUCT((MONTH(交易记录!B:B)=A8)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C8">SUMPRODUCT((MONTH(交易记录!B:B)=A8)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D8" s="11" t="e">
@@ -2446,7 +2644,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F8" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2466,11 +2664,11 @@
         <v>7</v>
       </c>
       <c r="B9" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A9)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A9)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C9" s="11" t="e">
-        <f t="array" ref="C9">SUMPRODUCT((MONTH(交易记录!B:B)=A9)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C9">SUMPRODUCT((MONTH(交易记录!B:B)=A9)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D9" s="11" t="e">
@@ -2478,7 +2676,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F9" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2498,11 +2696,11 @@
         <v>8</v>
       </c>
       <c r="B10" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A10)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A10)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C10" s="11" t="e">
-        <f t="array" ref="C10">SUMPRODUCT((MONTH(交易记录!B:B)=A10)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C10">SUMPRODUCT((MONTH(交易记录!B:B)=A10)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D10" s="11" t="e">
@@ -2510,7 +2708,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F10" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2530,11 +2728,11 @@
         <v>9</v>
       </c>
       <c r="B11" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A11)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A11)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C11" s="11" t="e">
-        <f t="array" ref="C11">SUMPRODUCT((MONTH(交易记录!B:B)=A11)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C11">SUMPRODUCT((MONTH(交易记录!B:B)=A11)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D11" s="11" t="e">
@@ -2542,7 +2740,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2562,11 +2760,11 @@
         <v>10</v>
       </c>
       <c r="B12" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A12)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A12)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C12" s="11" t="e">
-        <f t="array" ref="C12">SUMPRODUCT((MONTH(交易记录!B:B)=A12)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C12">SUMPRODUCT((MONTH(交易记录!B:B)=A12)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D12" s="11" t="e">
@@ -2574,7 +2772,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F12" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2594,11 +2792,11 @@
         <v>11</v>
       </c>
       <c r="B13" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A13)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A13)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C13" s="11" t="e">
-        <f t="array" ref="C13">SUMPRODUCT((MONTH(交易记录!B:B)=A13)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C13">SUMPRODUCT((MONTH(交易记录!B:B)=A13)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D13" s="11" t="e">
@@ -2606,7 +2804,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F13" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2626,11 +2824,11 @@
         <v>12</v>
       </c>
       <c r="B14" s="11" t="e">
-        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A14)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O&lt;&gt;""))</f>
+        <f>SUMPRODUCT((MONTH(交易记录!B:B)=A14)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P&lt;&gt;""))</f>
         <v>#VALUE!</v>
       </c>
       <c r="C14" s="11" t="e">
-        <f t="array" ref="C14">SUMPRODUCT((MONTH(交易记录!B:B)=A14)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!O:O="盈"))</f>
+        <f t="array" ref="C14">SUMPRODUCT((MONTH(交易记录!B:B)=A14)*(YEAR(交易记录!B:B)=$A$1)*(交易记录!P:P="盈"))</f>
         <v>#VALUE!</v>
       </c>
       <c r="D14" s="11" t="e">
@@ -2638,7 +2836,7 @@
         <v>#VALUE!</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F14" s="10" t="e">
         <f t="shared" si="1"/>
@@ -2673,12 +2871,12 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B2">
         <v>70000</v>
@@ -2686,7 +2884,7 @@
     </row>
     <row r="3" spans="1:5" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B3">
         <v>2100</v>
@@ -2694,24 +2892,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="8" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>88</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>90</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="E6" s="9" t="s">
         <v>91</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">

--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26E5F08-4AC5-4AD5-8A0A-14657317B72F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBD1504-E7B6-47F9-9A91-D8A804B7DB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交易记录" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="140">
   <si>
     <t>股票代码</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -929,7 +929,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>没看出很强，不懂里面逻辑，业绩估计也不是很好，所以清了</t>
+    <t>中信</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>没看出很强，不懂里面逻辑，业绩估计也不是很好，所以清了。卖完第二天就大涨7%，分时一直在黄线之上，就要拿稳。我觉得一个股票还是要拿久一点，起码要以半月为准，除非大涨后，我觉得还是得耐心持股</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>凯盛科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>短线</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>UTG玻璃，有商业航天概念，前一天涨停，说明有资金进入。有点买高了，我觉得还是得尾盘来买入，等它企稳。还是得等回踩后再来介入比较合适</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4.20补了一点仓 23.8，以为低点，还有更低点，还是太着急了，等待企稳后再买入会比较合适。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1380,7 +1400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U11"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" customWidth="1"/>
@@ -1496,7 +1516,7 @@
         <v>600</v>
       </c>
       <c r="I2" s="1">
-        <f t="shared" ref="I2:I11" si="0">F2*H2</f>
+        <f t="shared" ref="I2:I12" si="0">F2*H2</f>
         <v>26331.600000000002</v>
       </c>
       <c r="J2" s="1">
@@ -1580,11 +1600,11 @@
         <v>7.47</v>
       </c>
       <c r="L3" s="1">
-        <f t="shared" ref="L3:L11" si="2">IF(G3&lt;&gt;"",J3-I3-K3,"")</f>
+        <f t="shared" ref="L3:L12" si="2">IF(G3&lt;&gt;"",J3-I3-K3,"")</f>
         <v>-2762.6699999999969</v>
       </c>
       <c r="M3" s="11">
-        <f t="shared" ref="M3:M11" si="3">IF(G3&lt;&gt;"",L3/I3*100,"")</f>
+        <f t="shared" ref="M3:M12" si="3">IF(G3&lt;&gt;"",L3/I3*100,"")</f>
         <v>-11.61361515373167</v>
       </c>
       <c r="N3" s="1">
@@ -1668,7 +1688,7 @@
         <v>-4.7421392857142877</v>
       </c>
       <c r="P4" s="1" t="str">
-        <f t="shared" ref="P4:P11" si="5">IF(G4&lt;&gt;"",IF(L4&gt;0,"盈","亏"),"")</f>
+        <f t="shared" ref="P4:P12" si="5">IF(G4&lt;&gt;"",IF(L4&gt;0,"盈","亏"),"")</f>
         <v>亏</v>
       </c>
       <c r="Q4" s="1">
@@ -1749,7 +1769,7 @@
         <v>0.37580000000000024</v>
       </c>
       <c r="R5" s="1">
-        <f t="shared" ref="R5:R11" si="7">IF(F5&lt;&gt;"",(I5-K5-N5)/H5,"")</f>
+        <f t="shared" ref="R5:R12" si="7">IF(F5&lt;&gt;"",(I5-K5-N5)/H5,"")</f>
         <v>12.827857142857143</v>
       </c>
       <c r="S5" s="2" t="s">
@@ -2121,7 +2141,7 @@
         <v>133</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.2">
@@ -2138,14 +2158,14 @@
         <v>132</v>
       </c>
       <c r="F11" s="2">
-        <v>24.651</v>
+        <v>24.204000000000001</v>
       </c>
       <c r="H11" s="2">
-        <v>800</v>
+        <v>1700</v>
       </c>
       <c r="I11" s="2">
         <f t="shared" si="0"/>
-        <v>19720.8</v>
+        <v>41146.800000000003</v>
       </c>
       <c r="L11" s="2" t="str">
         <f t="shared" si="2"/>
@@ -2164,7 +2184,62 @@
       </c>
       <c r="R11" s="2">
         <f t="shared" si="7"/>
-        <v>22.151</v>
+        <v>23.027529411764707</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="B12" s="16">
+        <v>46132</v>
+      </c>
+      <c r="D12" s="2">
+        <v>600552</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F12" s="2">
+        <v>15.378</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2500</v>
+      </c>
+      <c r="I12" s="2">
+        <f t="shared" si="0"/>
+        <v>38445</v>
+      </c>
+      <c r="L12" s="2" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="M12" s="2" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="N12" s="2">
+        <v>2400</v>
+      </c>
+      <c r="P12" s="2" t="str">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="R12" s="2">
+        <f t="shared" si="7"/>
+        <v>14.417999999999999</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>138</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +2390,7 @@
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
-        <v>-1719.2965587301594</v>
+        <v>-1758.3714805194813</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -2371,7 +2446,7 @@
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>36</v>
@@ -2383,7 +2458,7 @@
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f>SUMIF(交易记录!G:G,"",交易记录!I:I)</f>
-        <v>19720.8</v>
+        <v>79591.8</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>37</v>

--- a/LearningNote/散户终极交易记录.xlsx
+++ b/LearningNote/散户终极交易记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\MyKnowledgeRepository\LearningNote\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBD1504-E7B6-47F9-9A91-D8A804B7DB63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6121E0C4-1686-4D6B-9F2A-A124D914F50B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="300" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="交易记录" sheetId="1" r:id="rId1"/>
@@ -1520,7 +1520,7 @@
         <v>26331.600000000002</v>
       </c>
       <c r="J2" s="1">
-        <f t="shared" ref="J2:J10" si="1">G2*H2</f>
+        <f t="shared" ref="J2:J11" si="1">G2*H2</f>
         <v>28650</v>
       </c>
       <c r="K2" s="1">
@@ -1684,7 +1684,7 @@
         <v>2800</v>
       </c>
       <c r="O4" s="1">
-        <f t="shared" ref="O4:O10" si="4">IF(G4&lt;&gt;"",L4/N4,"")</f>
+        <f t="shared" ref="O4:O11" si="4">IF(G4&lt;&gt;"",L4/N4,"")</f>
         <v>-4.7421392857142877</v>
       </c>
       <c r="P4" s="1" t="str">
@@ -1692,7 +1692,7 @@
         <v>亏</v>
       </c>
       <c r="Q4" s="1">
-        <f t="shared" ref="Q4:Q10" si="6">IF(G4&lt;&gt;"",IF(L4&gt;0,ABS(L4)/N4,ABS(L4)/N4),"")</f>
+        <f t="shared" ref="Q4:Q11" si="6">IF(G4&lt;&gt;"",IF(L4&gt;0,ABS(L4)/N4,ABS(L4)/N4),"")</f>
         <v>4.7421392857142877</v>
       </c>
       <c r="R4" s="1">
@@ -2151,6 +2151,9 @@
       <c r="B11" s="16">
         <v>46128</v>
       </c>
+      <c r="C11" s="16">
+        <v>46134</v>
+      </c>
       <c r="D11" s="2">
         <v>600602</v>
       </c>
@@ -2159,6 +2162,9 @@
       </c>
       <c r="F11" s="2">
         <v>24.204000000000001</v>
+      </c>
+      <c r="G11" s="2">
+        <v>22.76</v>
       </c>
       <c r="H11" s="2">
         <v>1700</v>
@@ -2167,20 +2173,32 @@
         <f t="shared" si="0"/>
         <v>41146.800000000003</v>
       </c>
-      <c r="L11" s="2" t="str">
+      <c r="J11" s="2">
+        <f t="shared" si="1"/>
+        <v>38692</v>
+      </c>
+      <c r="L11" s="2">
         <f t="shared" si="2"/>
-        <v/>
-      </c>
-      <c r="M11" s="2" t="str">
+        <v>-2454.8000000000029</v>
+      </c>
+      <c r="M11" s="2">
         <f t="shared" si="3"/>
-        <v/>
+        <v>-5.9659560403239196</v>
       </c>
       <c r="N11" s="2">
         <v>2000</v>
       </c>
+      <c r="O11" s="2">
+        <f t="shared" si="4"/>
+        <v>-1.2274000000000014</v>
+      </c>
       <c r="P11" s="2" t="str">
         <f t="shared" si="5"/>
-        <v/>
+        <v>亏</v>
+      </c>
+      <c r="Q11" s="2">
+        <f t="shared" si="6"/>
+        <v>1.2274000000000014</v>
       </c>
       <c r="R11" s="2">
         <f t="shared" si="7"/>
@@ -2270,7 +2288,7 @@
     <row r="2" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <f>COUNTIF(交易记录!P:P,"盈")+COUNTIF(交易记录!P:P,"亏")</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>21</v>
@@ -2294,7 +2312,7 @@
     <row r="4" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="6">
         <f>COUNTIF(交易记录!P:P,"亏")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>23</v>
@@ -2306,7 +2324,7 @@
     <row r="5" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(A2&gt;0,A3/A2*100,"0")</f>
-        <v>44.444444444444443</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>24</v>
@@ -2318,7 +2336,7 @@
     <row r="6" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <f>SUM(交易记录!L:L)</f>
-        <v>-18263.710000000017</v>
+        <v>-20718.51000000002</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>25</v>
@@ -2330,7 +2348,7 @@
     <row r="7" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <f>IF(A2&gt;0,A6/A2,"0")</f>
-        <v>-2029.301111111113</v>
+        <v>-2071.8510000000019</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>26</v>
@@ -2354,7 +2372,7 @@
     <row r="9" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <f>IF(A4&gt;0,ABS(AVERAGEIF(交易记录!O:O,"&lt;0",交易记录!O:O)),"0")</f>
-        <v>2.4005998571428568</v>
+        <v>2.2050665476190479</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>28</v>
@@ -2366,7 +2384,7 @@
     <row r="10" spans="1:3" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <f>IF(A9&gt;0,A8/A9,"0")</f>
-        <v>0.41070949984980892</v>
+        <v>0.44712898471534029</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>29</v>
@@ -2378,7 +2396,7 @@
     <row r="11" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f>IF(A2&gt;0,(A5/100)*A8 - (1-A5/100)*A9,"0")</f>
-        <v>-0.89546695767195805</v>
+        <v>-0.92866026190476259</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>30</v>
@@ -2390,7 +2408,7 @@
     <row r="12" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <f>IF(A2&gt;0,A11*AVERAGEIF(交易记录!N:N,"&gt;0",交易记录!N:N),"0")</f>
-        <v>-1758.3714805194813</v>
+        <v>-1823.5510597402613</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>31</v>
@@ -2402,7 +2420,7 @@
     <row r="13" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <f>SUM(交易记录!O:O)</f>
-        <v>-8.0592026190476247</v>
+        <v>-9.2866026190476259</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>32</v>
@@ -2446,7 +2464,7 @@
     <row r="17" spans="1:3" ht="15.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <f>COUNTA(交易记录!A:A)-1-A2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>36</v>
@@ -2458,7 +2476,7 @@
     <row r="18" spans="1:3" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <f>SUMIF(交易记录!G:G,"",交易记录!I:I)</f>
-        <v>79591.8</v>
+        <v>38445</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>37</v>
